--- a/Triple/publication_plots_triple/supplementary_model_selection_table.xlsx
+++ b/Triple/publication_plots_triple/supplementary_model_selection_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Dataset</t>
   </si>
@@ -67,49 +67,43 @@
     <t>N_Unique_Selected_Features</t>
   </si>
   <si>
-    <t>ADC_Post1_Post2</t>
+    <t>ADC_Post1_Pre</t>
+  </si>
+  <si>
+    <t>elasticnet_then_mrmr_auto_k_no_smote</t>
   </si>
   <si>
     <t>elasticnet_then_mrmr_auto_k_smote</t>
   </si>
   <si>
-    <t>elasticnet_then_mrmr_auto_k_no_smote</t>
+    <t>mrmr_then_elasticnet_no_corr_auto_k_no_smote</t>
+  </si>
+  <si>
+    <t>mrmr_then_elasticnet_no_corr_auto_k_smote</t>
   </si>
   <si>
     <t>corr_mrmr_auto_k_smote</t>
   </si>
   <si>
-    <t>mrmr_then_elasticnet_no_corr_auto_k_no_smote</t>
-  </si>
-  <si>
-    <t>mrmr_then_elasticnet_no_corr_auto_k_smote</t>
-  </si>
-  <si>
     <t>corr_mrmr_auto_k_no_smote</t>
   </si>
   <si>
     <t>elasticnet_then_mrmr</t>
   </si>
   <si>
+    <t>mrmr_then_elasticnet_no_corr</t>
+  </si>
+  <si>
     <t>corr_mrmr</t>
   </si>
   <si>
-    <t>mrmr_then_elasticnet_no_corr</t>
-  </si>
-  <si>
     <t>auto</t>
   </si>
   <si>
+    <t>SVM_Linear</t>
+  </si>
+  <si>
     <t>LogisticRegression</t>
-  </si>
-  <si>
-    <t>SVM_Linear</t>
-  </si>
-  <si>
-    <t>NaiveBayes</t>
-  </si>
-  <si>
-    <t>SVM_RBF</t>
   </si>
 </sst>
 </file>
@@ -537,43 +531,43 @@
         <v>27</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
       </c>
       <c r="G2">
-        <v>0.797</v>
+        <v>0.836</v>
       </c>
       <c r="H2">
-        <v>0.075</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I2">
-        <v>0.79</v>
+        <v>0.799</v>
       </c>
       <c r="J2">
-        <v>0.837</v>
+        <v>0.879</v>
       </c>
       <c r="K2">
-        <v>0.841</v>
+        <v>0.832</v>
       </c>
       <c r="L2">
-        <v>0.726</v>
+        <v>0.735</v>
       </c>
       <c r="M2">
-        <v>0.719</v>
+        <v>0.713</v>
       </c>
       <c r="N2">
-        <v>0.748</v>
+        <v>0.751</v>
       </c>
       <c r="O2">
-        <v>0.733</v>
+        <v>0.746</v>
       </c>
       <c r="P2">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q2">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -590,43 +584,43 @@
         <v>27</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0.795</v>
+        <v>0.823</v>
       </c>
       <c r="H3">
         <v>0.08</v>
       </c>
       <c r="I3">
-        <v>0.759</v>
+        <v>0.801</v>
       </c>
       <c r="J3">
-        <v>0.834</v>
+        <v>0.868</v>
       </c>
       <c r="K3">
-        <v>0.789</v>
+        <v>0.833</v>
       </c>
       <c r="L3">
-        <v>0.736</v>
+        <v>0.723</v>
       </c>
       <c r="M3">
-        <v>0.715</v>
+        <v>0.713</v>
       </c>
       <c r="N3">
-        <v>0.776</v>
+        <v>0.721</v>
       </c>
       <c r="O3">
-        <v>0.767</v>
+        <v>0.718</v>
       </c>
       <c r="P3">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q3">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -643,43 +637,43 @@
         <v>27</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="H4">
-        <v>0.07199999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="I4">
-        <v>0.766</v>
+        <v>0.717</v>
       </c>
       <c r="J4">
-        <v>0.829</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K4">
-        <v>0.8139999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="L4">
-        <v>0.694</v>
+        <v>0.724</v>
       </c>
       <c r="M4">
-        <v>0.6929999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="N4">
-        <v>0.712</v>
+        <v>0.745</v>
       </c>
       <c r="O4">
-        <v>0.706</v>
+        <v>0.738</v>
       </c>
       <c r="P4">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q4">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -690,49 +684,49 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0.786</v>
+        <v>0.77</v>
       </c>
       <c r="H5">
-        <v>0.054</v>
+        <v>0.116</v>
       </c>
       <c r="I5">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="J5">
-        <v>0.831</v>
+        <v>0.824</v>
       </c>
       <c r="K5">
-        <v>0.755</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="L5">
-        <v>0.6870000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M5">
-        <v>0.681</v>
+        <v>0.673</v>
       </c>
       <c r="N5">
-        <v>0.705</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O5">
-        <v>0.705</v>
+        <v>0.694</v>
       </c>
       <c r="P5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q5">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -752,40 +746,40 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0.784</v>
+        <v>0.719</v>
       </c>
       <c r="H6">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I6">
-        <v>0.76</v>
+        <v>0.677</v>
       </c>
       <c r="J6">
-        <v>0.838</v>
+        <v>0.795</v>
       </c>
       <c r="K6">
-        <v>0.819</v>
+        <v>0.722</v>
       </c>
       <c r="L6">
-        <v>0.724</v>
+        <v>0.623</v>
       </c>
       <c r="M6">
-        <v>0.703</v>
+        <v>0.6</v>
       </c>
       <c r="N6">
-        <v>0.713</v>
+        <v>0.637</v>
       </c>
       <c r="O6">
-        <v>0.712</v>
+        <v>0.634</v>
       </c>
       <c r="P6">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="Q6">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -796,7 +790,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -808,37 +802,37 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>0.777</v>
+        <v>0.713</v>
       </c>
       <c r="H7">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="I7">
-        <v>0.757</v>
+        <v>0.648</v>
       </c>
       <c r="J7">
-        <v>0.828</v>
+        <v>0.795</v>
       </c>
       <c r="K7">
-        <v>0.8090000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="L7">
-        <v>0.6889999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="M7">
-        <v>0.677</v>
+        <v>0.579</v>
       </c>
       <c r="N7">
-        <v>0.6919999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="O7">
-        <v>0.6840000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="P7">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="Q7">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
